--- a/docs/testdaten/testdaten_darlehensregister.xlsx
+++ b/docs/testdaten/testdaten_darlehensregister.xlsx
@@ -773,7 +773,7 @@
         <v>IM-2024-005</v>
       </c>
       <c r="G7">
-        <v>2800000</v>
+        <v>2000000</v>
       </c>
       <c r="H7" t="str">
         <v>10.05.2024</v>
@@ -832,7 +832,7 @@
         <v>IM-2025-006</v>
       </c>
       <c r="G8">
-        <v>3200000</v>
+        <v>2200000</v>
       </c>
       <c r="H8" t="str">
         <v>20.08.2025</v>
